--- a/output/graficos_dimensiones/comunal_migracion_flujos_od_2022_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_migracion_flujos_od_2022_nuble.xlsx
@@ -438,7 +438,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 09:31</t>
+    <t xml:space="preserve">2026-09-18 14:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_migracion_flujos_od_2022_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_migracion_flujos_od_2022_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">202</t>
   </si>
   <si>
-    <t xml:space="preserve">Ranquil</t>
+    <t xml:space="preserve">Ránquil</t>
   </si>
   <si>
     <t xml:space="preserve">117</t>
@@ -438,7 +438,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:11</t>
+    <t xml:space="preserve">2026-10-05 04:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
